--- a/stores picture/家福拉麵.xlsx
+++ b/stores picture/家福拉麵.xlsx
@@ -616,144 +616,144 @@
     <col min="4" max="4" width="42.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="47" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
@@ -764,7 +764,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
@@ -775,7 +775,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -783,7 +783,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -791,7 +791,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -799,7 +799,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -807,7 +807,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -815,7 +815,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -823,7 +823,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -831,7 +831,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -839,7 +839,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -847,7 +847,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -855,7 +855,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -863,7 +863,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -871,7 +871,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -879,7 +879,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -887,7 +887,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -895,7 +895,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -903,7 +903,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
         <v>41</v>
@@ -914,7 +914,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
         <v>41</v>
@@ -925,7 +925,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
         <v>41</v>
@@ -936,7 +936,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D34" t="s">
         <v>41</v>
@@ -947,7 +947,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D35" t="s">
         <v>41</v>
@@ -958,7 +958,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>41</v>
@@ -969,7 +969,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D37" t="s">
         <v>41</v>
@@ -980,7 +980,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D38" t="s">
         <v>41</v>
@@ -991,7 +991,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="1">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="D39" t="s">
         <v>41</v>
@@ -1002,7 +1002,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="1">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>41</v>
@@ -1013,7 +1013,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1021,7 +1021,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1029,7 +1029,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1037,7 +1037,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1045,7 +1045,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1053,7 +1053,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1061,7 +1061,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1069,7 +1069,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1077,7 +1077,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1085,7 +1085,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1093,7 +1093,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1101,7 +1101,7 @@
         <v>53</v>
       </c>
       <c r="B52" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1109,7 +1109,7 @@
         <v>54</v>
       </c>
       <c r="B53" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1117,7 +1117,7 @@
         <v>55</v>
       </c>
       <c r="B54" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1125,7 +1125,7 @@
         <v>56</v>
       </c>
       <c r="B55" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
